--- a/IlNufuslarii.xlsx
+++ b/IlNufuslarii.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t>Adana</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>Nüfus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net Göç</t>
   </si>
 </sst>
 </file>
@@ -686,6 +689,9 @@
       <c r="B1" s="7" t="s">
         <v>83</v>
       </c>
+      <c r="C1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="2" ht="17.100000000000001" customHeight="1">
       <c r="A2" s="1" t="s">
